--- a/StructureDefinition-Referens.xlsx
+++ b/StructureDefinition-Referens.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Referens.xlsx
+++ b/StructureDefinition-Referens.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Referens).</t>
+    <t>Klassen Referens håller information om vilket referensintervall eller referensvärde som gäller för ett resultat.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -254,6 +254,10 @@
     <t>Source attribute: intervall</t>
   </si>
   <si>
+    <t>Angivelse av referensintervall som numeriskt värde av mätvärden. Ett referensvärde anges genom att antingen ange ett intervall från det lägre värdet 0 till det högre värdet som sätts till referensvärdet, alternativt från referensvärde som start på intervallet utan angivelse av intervallets slut för att ange att normalvärde ligger över referensvärdet.
+Ett och endast ett av attributen intervall eller text ska anges.</t>
+  </si>
+  <si>
     <t>Referens.text</t>
   </si>
   <si>
@@ -264,16 +268,26 @@
     <t>Source attribute: text</t>
   </si>
   <si>
+    <t>Textuell beskrivning av referensintervall.
+Ett och endast ett av attributen intervall eller text ska anges.</t>
+  </si>
+  <si>
     <t>Referens.population</t>
   </si>
   <si>
     <t>Source attribute: population</t>
   </si>
   <si>
+    <t>Angivelse av den referenspopulation som ligger till grund för angivet referensintervall.</t>
+  </si>
+  <si>
     <t>Referens.kommentar</t>
   </si>
   <si>
     <t>Source attribute: kommentar</t>
+  </si>
+  <si>
+    <t>Angivelse av kommentar för det angivna referensintervallet.</t>
   </si>
   <si>
     <t>Referens.jamforsMed</t>
@@ -869,7 +883,7 @@
         <v>78</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -937,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -963,13 +977,13 @@
         <v>19</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1020,7 +1034,7 @@
         <v>19</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>71</v>
@@ -1037,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1063,13 +1077,13 @@
         <v>19</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1120,7 +1134,7 @@
         <v>19</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>71</v>
@@ -1137,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1163,13 +1177,13 @@
         <v>19</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1220,7 +1234,7 @@
         <v>19</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>71</v>
@@ -1237,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1263,13 +1277,13 @@
         <v>19</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1320,7 +1334,7 @@
         <v>19</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>71</v>
